--- a/data/trans_orig/P21D4_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P21D4_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitándolo, no pudo recibir atención médica mental (psicólogo) en 2023</t>
+          <t>Población que, necesitándolo, no pudo recibir atención médica mental (psicólogo) en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>180195</t>
+          <t>181211</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>202100</t>
+          <t>202180</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>112693</t>
+          <t>113079</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>134028</t>
+          <t>134065</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>301610</t>
+          <t>302957</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>331673</t>
+          <t>332967</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1849</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23754</t>
+          <t>22738</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4653</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22675</t>
+          <t>24838</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10222</t>
+          <t>9804</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38867</t>
+          <t>37306</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -956,97 +956,97 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2688</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4544</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>13437</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>9,57%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>2688</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>13341</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>13809</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>9,51%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>2688</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>15707</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -1069,97 +1069,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4544</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2861</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3690</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>175894</t>
+          <t>176888</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>197857</t>
+          <t>198156</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>268721</t>
+          <t>266618</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>286310</t>
+          <t>285854</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>451422</t>
+          <t>451142</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>480596</t>
+          <t>481530</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,11%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>5633</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26363</t>
+          <t>26417</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18515</t>
+          <t>20155</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12062</t>
+          <t>11918</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39151</t>
+          <t>39660</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>7858</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>852</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9491</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -1638,97 +1638,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2498</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2689</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>10837</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>3,72%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>2498</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>9347</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>9367</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>2498</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>8313</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>195473</t>
+          <t>195163</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>211435</t>
+          <t>211229</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>232064</t>
+          <t>231623</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>245663</t>
+          <t>245583</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>433893</t>
+          <t>434904</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>452744</t>
+          <t>454120</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4051</t>
+          <t>4257</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20013</t>
+          <t>20323</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9768</t>
+          <t>9713</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23141</t>
+          <t>22865</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>17693</t>
+          <t>16794</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>36469</t>
+          <t>35863</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -2094,97 +2094,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1854</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>862</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>162</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>969</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>1028</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,03%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>810</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,03%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,22%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>639</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>700</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>5822</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>82984</t>
+          <t>86706</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>486488</t>
+          <t>489272</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>285524</t>
+          <t>284555</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>300959</t>
+          <t>300920</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>244713</t>
+          <t>264332</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>783487</t>
+          <t>781228</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,19%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30792</t>
+          <t>28683</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>441523</t>
+          <t>437321</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13726</t>
+          <t>13478</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>27207</t>
+          <t>27973</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>48464</t>
+          <t>49146</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>602003</t>
+          <t>576532</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>68,03%</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11730</t>
+          <t>10997</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2519</t>
+          <t>2422</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9866</t>
+          <t>9813</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2614</t>
+          <t>2981</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>16907</t>
+          <t>16712</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>608</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5385</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>640</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8347</t>
+          <t>8757</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>206583</t>
+          <t>205898</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>223646</t>
+          <t>223570</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>188934</t>
+          <t>188777</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>203930</t>
+          <t>203458</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>399642</t>
+          <t>401757</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>423941</t>
+          <t>424770</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,31%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9249</t>
+          <t>9169</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25560</t>
+          <t>24258</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17249</t>
+          <t>17699</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>30697</t>
+          <t>31221</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30071</t>
+          <t>30269</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>51359</t>
+          <t>50216</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>1730</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10536</t>
+          <t>11002</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>731</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7213</t>
+          <t>6549</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13323</t>
+          <t>14020</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>5943</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>7712</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2346</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>10447</t>
+          <t>10350</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>145617</t>
+          <t>145983</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>153673</t>
+          <t>153812</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>159387</t>
+          <t>159264</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>171325</t>
+          <t>170784</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>309410</t>
+          <t>308440</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>322997</t>
+          <t>322962</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,54%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9286</t>
+          <t>9628</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10656</t>
+          <t>10664</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>21708</t>
+          <t>21124</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>14312</t>
+          <t>14538</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>26808</t>
+          <t>28117</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4051</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>577</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>5820</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>934</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>5777</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>109215</t>
+          <t>109464</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>116219</t>
+          <t>116199</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>154964</t>
+          <t>155074</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>163519</t>
+          <t>163575</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>266726</t>
+          <t>267250</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>278129</t>
+          <t>278185</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7493</t>
+          <t>7771</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>4376</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>11488</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>16716</t>
+          <t>16275</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -4375,7 +4375,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2720</t>
+          <t>2675</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>993</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6604</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7342</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,62 +4518,62 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>946</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>3595</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>3218</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>802902</t>
+          <t>828706</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1565734</t>
+          <t>1568296</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1439505</t>
+          <t>1439125</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1483893</t>
+          <t>1482893</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>2126661</t>
+          <t>2136189</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3024900</t>
+          <t>3025062</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>80366</t>
+          <t>78781</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>854336</t>
+          <t>825986</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>83613</t>
+          <t>86001</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>123125</t>
+          <t>122883</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>184223</t>
+          <t>184734</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1093766</t>
+          <t>1078507</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,13%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>5424</t>
+          <t>5547</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>20295</t>
+          <t>21209</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>9243</t>
+          <t>9070</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>25749</t>
+          <t>25261</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>17796</t>
+          <t>17485</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>41642</t>
+          <t>39242</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>796</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>8695</t>
+          <t>9442</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>20783</t>
+          <t>21203</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>10170</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>24816</t>
+          <t>26447</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D4_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P21D4_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>195850</t>
+          <t>203185</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>181211</t>
+          <t>189218</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>202180</t>
+          <t>209114</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>125846</t>
+          <t>146009</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>113079</t>
+          <t>133096</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>134065</t>
+          <t>154949</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>321695</t>
+          <t>349194</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>302957</t>
+          <t>330133</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>332967</t>
+          <t>361144</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8099</t>
+          <t>7596</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>1667</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22738</t>
+          <t>21563</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11812</t>
+          <t>14604</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4778</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24838</t>
+          <t>27391</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>19911</t>
+          <t>22201</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9804</t>
+          <t>10492</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37306</t>
+          <t>41200</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13437</t>
+          <t>12099</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2688</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13809</t>
+          <t>11499</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>203949</t>
+          <t>210781</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>140346</t>
+          <t>162985</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>344294</t>
+          <t>373766</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>189403</t>
+          <t>209703</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>176888</t>
+          <t>196407</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>198156</t>
+          <t>219173</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>278379</t>
+          <t>236515</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>266618</t>
+          <t>226694</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>285854</t>
+          <t>242400</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>467782</t>
+          <t>446217</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>451142</t>
+          <t>429808</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>481530</t>
+          <t>457514</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>95,88%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>13697</t>
+          <t>15290</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5633</t>
+          <t>6306</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26417</t>
+          <t>27781</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10080</t>
+          <t>10240</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20155</t>
+          <t>17854</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>23777</t>
+          <t>25531</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11918</t>
+          <t>14983</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39660</t>
+          <t>40536</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>9053</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>6655</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1783</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>11895</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2498</t>
+          <t>2503</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10837</t>
+          <t>9878</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2498</t>
+          <t>2503</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9367</t>
+          <t>9365</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>204722</t>
+          <t>226813</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>291119</t>
+          <t>250354</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>477166</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>477166</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>495841</t>
+          <t>477166</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>205628</t>
+          <t>242124</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>195163</t>
+          <t>231982</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>211229</t>
+          <t>248109</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>239671</t>
+          <t>275303</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>231623</t>
+          <t>266151</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>245583</t>
+          <t>281801</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>445299</t>
+          <t>517427</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>434904</t>
+          <t>505442</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>454120</t>
+          <t>526981</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9858</t>
+          <t>10394</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4257</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20323</t>
+          <t>20536</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15326</t>
+          <t>17706</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9713</t>
+          <t>11510</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22865</t>
+          <t>25929</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>25184</t>
+          <t>28100</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>16794</t>
+          <t>18878</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>35863</t>
+          <t>39968</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>962</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>4686</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>962</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>5338</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>798</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>6325</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,22 +2272,22 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>819</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5822</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>252518</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>257689</t>
+          <t>296635</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>473175</t>
+          <t>549153</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>258049</t>
+          <t>289971</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>86706</t>
+          <t>276421</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>489272</t>
+          <t>299026</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>294073</t>
+          <t>317430</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>284555</t>
+          <t>307201</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>300920</t>
+          <t>324518</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>552121</t>
+          <t>607401</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>264332</t>
+          <t>593150</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>781228</t>
+          <t>619406</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>93,44%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>263357</t>
+          <t>21684</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28683</t>
+          <t>13439</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>437321</t>
+          <t>34034</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>19599</t>
+          <t>21063</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13478</t>
+          <t>14819</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>27973</t>
+          <t>29669</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>282956</t>
+          <t>42747</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>49146</t>
+          <t>32506</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>576532</t>
+          <t>56200</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10997</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,22 +2693,22 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2422</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9813</t>
+          <t>10713</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>9200</t>
+          <t>9539</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2981</t>
+          <t>5177</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>16712</t>
+          <t>16539</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6401</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,77 +2796,77 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>2044</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5484</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>3188</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>8056</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>1,22%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>608</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>5385</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>3142</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>640</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>8757</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>526558</t>
+          <t>317068</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>526558</t>
+          <t>317068</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>526558</t>
+          <t>317068</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>320862</t>
+          <t>345808</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>320862</t>
+          <t>345808</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>320862</t>
+          <t>345808</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>847419</t>
+          <t>662875</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>847419</t>
+          <t>662875</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>847419</t>
+          <t>662875</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>216158</t>
+          <t>234637</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>205898</t>
+          <t>224339</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>223570</t>
+          <t>241991</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>197241</t>
+          <t>221420</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>188777</t>
+          <t>213214</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>203458</t>
+          <t>228661</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,27 +3071,27 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>413399</t>
+          <t>456056</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>401757</t>
+          <t>441873</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>424770</t>
+          <t>466534</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>15883</t>
+          <t>16458</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9169</t>
+          <t>10163</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24258</t>
+          <t>25243</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>23374</t>
+          <t>25526</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17699</t>
+          <t>18634</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31221</t>
+          <t>33039</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>39257</t>
+          <t>41984</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30269</t>
+          <t>32715</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>50216</t>
+          <t>54289</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1730</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11002</t>
+          <t>9860</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>699</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6549</t>
+          <t>6704</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>7453</t>
+          <t>7398</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14020</t>
+          <t>13831</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3350,12 +3350,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>3841</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>5087</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2362</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>10350</t>
+          <t>10572</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>238504</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>238504</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>238504</t>
+          <t>257481</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>226692</t>
+          <t>253453</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>226692</t>
+          <t>253453</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>226692</t>
+          <t>253453</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>465196</t>
+          <t>510934</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>465196</t>
+          <t>510934</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>465196</t>
+          <t>510934</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>150686</t>
+          <t>167741</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>145983</t>
+          <t>161499</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>153812</t>
+          <t>171084</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>165920</t>
+          <t>177688</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>159264</t>
+          <t>170179</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>170784</t>
+          <t>183628</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>316606</t>
+          <t>345430</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>308440</t>
+          <t>336997</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>322962</t>
+          <t>352512</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,5%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>5386</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>9628</t>
+          <t>11461</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>15576</t>
+          <t>16715</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10664</t>
+          <t>11636</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>21124</t>
+          <t>23724</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>20367</t>
+          <t>22101</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>14538</t>
+          <t>16011</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>28117</t>
+          <t>30104</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>926</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3806,12 +3806,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>2274</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5820</t>
+          <t>5889</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2620</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5629</t>
+          <t>7093</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,22 +3979,22 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>2620</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5777</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>156354</t>
+          <t>174053</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>185277</t>
+          <t>198981</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>185277</t>
+          <t>198981</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>185277</t>
+          <t>198981</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>341631</t>
+          <t>373035</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>341631</t>
+          <t>373035</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>341631</t>
+          <t>373035</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>113707</t>
+          <t>124514</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>109464</t>
+          <t>120266</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>116199</t>
+          <t>127241</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>159808</t>
+          <t>174881</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>155074</t>
+          <t>169150</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>163575</t>
+          <t>179253</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>273517</t>
+          <t>299395</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>267250</t>
+          <t>293224</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>278185</t>
+          <t>305126</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,64%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>3933</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1672</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7771</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,17 +4287,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>4179</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>11711</t>
+          <t>13459</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>10809</t>
+          <t>12036</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>7412</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>16275</t>
+          <t>17252</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>528</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4375,12 +4375,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2675</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2836</t>
+          <t>3175</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5976</t>
+          <t>7651</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,17 +4435,17 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>3360</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>8278</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>586</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4488,12 +4488,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>586</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>118206</t>
+          <t>129561</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>170049</t>
+          <t>186159</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>170049</t>
+          <t>186159</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>170049</t>
+          <t>186159</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>288256</t>
+          <t>315720</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>288256</t>
+          <t>315720</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>288256</t>
+          <t>315720</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>1329482</t>
+          <t>1471874</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>828706</t>
+          <t>1445332</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1568296</t>
+          <t>1492768</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>1460937</t>
+          <t>1549245</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1439125</t>
+          <t>1527462</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1482893</t>
+          <t>1568694</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>2790419</t>
+          <t>3021119</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>2136189</t>
+          <t>2987565</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3025062</t>
+          <t>3047101</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>93,39%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>319090</t>
+          <t>80741</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>78781</t>
+          <t>61816</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>825986</t>
+          <t>106024</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>103172</t>
+          <t>113957</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>86001</t>
+          <t>96882</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>122883</t>
+          <t>133502</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>422262</t>
+          <t>194698</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>184734</t>
+          <t>168733</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>1078507</t>
+          <t>223399</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>11825</t>
+          <t>12274</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>5547</t>
+          <t>6079</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>21209</t>
+          <t>21208</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>14859</t>
+          <t>16890</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>9070</t>
+          <t>10710</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>25261</t>
+          <t>27816</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>26684</t>
+          <t>29164</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>17485</t>
+          <t>20270</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>39242</t>
+          <t>43107</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>1149</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>9442</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,67 +5082,67 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>13066</t>
+          <t>14282</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>7828</t>
+          <t>8822</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>21203</t>
+          <t>21994</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>17667</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>11739</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>26607</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
           <t>0,82%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>16447</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>10170</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>26447</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>1592034</t>
+          <t>1694374</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>3255812</t>
+          <t>3262648</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>3255812</t>
+          <t>3262648</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3255812</t>
+          <t>3262648</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
